--- a/매출전표_정제.xlsx
+++ b/매출전표_정제.xlsx
@@ -419,7 +419,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="3" t="str">
-        <x:v>교육용 가상 표본 | 2026.09.01–09.30 | 민승환 · 학번 미입력</x:v>
+        <x:v>교육용 가상 표본 | 2026.09.01–09.30 | 민승환 · 학번 2021308</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
